--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488107_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488107_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9743</v>
+        <v>4.9796</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3426</v>
+        <v>3.2637</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6317</v>
+        <v>1.7159</v>
       </c>
       <c r="G2" t="n">
         <v>2.6809</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4233</v>
+        <v>0.4286</v>
       </c>
       <c r="T2" t="n">
-        <v>0.191</v>
+        <v>0.112</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2323</v>
+        <v>0.3166</v>
       </c>
       <c r="V2" t="n">
         <v>1.4737</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7912</v>
+        <v>1.4204</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5213</v>
+        <v>-0.2707</v>
       </c>
       <c r="F3" t="n">
-        <v>1.27</v>
+        <v>1.6911</v>
       </c>
       <c r="G3" t="n">
         <v>0.2525</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>1.184</v>
+        <v>0.8131</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8629</v>
+        <v>0.0708</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3211</v>
+        <v>0.7423</v>
       </c>
       <c r="V3" t="n">
         <v>1.5441</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0375</v>
+        <v>1.3089</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4053</v>
+        <v>-0.4293</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6322</v>
+        <v>1.7382</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.1113</v>
+        <v>-1.0478</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0394</v>
+        <v>-0.1831</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0719</v>
+        <v>-0.8647</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2076</v>
+        <v>-0.5919</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6211</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.8287</v>
+        <v>-1.2779</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9037</v>
+        <v>-0.456</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6605</v>
+        <v>-0.8691</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2431</v>
+        <v>0.4132</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8932</v>
+        <v>0.5727</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0658</v>
+        <v>0.1625</v>
       </c>
       <c r="U4" t="n">
-        <v>0.959</v>
+        <v>0.4102</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0663</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6698</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7218</v>
+        <v>0.7996</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1519</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8737</v>
+        <v>0.7165</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5123</v>
+        <v>-2.1113</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9927</v>
+        <v>-0.0394</v>
       </c>
       <c r="I5" t="n">
-        <v>3.505</v>
+        <v>-2.0719</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2103</v>
+        <v>-0.2076</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5379</v>
+        <v>1.6211</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7482</v>
+        <v>-1.8287</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.698</v>
+        <v>-1.9037</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4548</v>
+        <v>-1.6605</v>
       </c>
       <c r="O5" t="n">
         <v>-0.2431</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
         <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2095</v>
+        <v>0.6553</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3889</v>
+        <v>-0.388</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5984</v>
+        <v>1.0433</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2071</v>
+        <v>1.0663</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6698</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3306</v>
+        <v>0.6546</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2672</v>
+        <v>0.3349</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5978</v>
+        <v>0.3197</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0478</v>
+        <v>0.2208</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1831</v>
+        <v>-0.8643</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8647</v>
+        <v>1.0851</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5919</v>
+        <v>1.189</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.1211</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2779</v>
+        <v>1.068</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.456</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8691</v>
+        <v>-0.9853</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>0.0171</v>
       </c>
       <c r="P6" t="n">
-        <v>1.784</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4056</v>
+        <v>-0.1807</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6753</v>
+        <v>-0.6826</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2698</v>
+        <v>0.5019</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.0109</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3868</v>
+        <v>0.2463</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6528</v>
+        <v>-1.16</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2659</v>
+        <v>1.4063</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0437</v>
@@ -1000,13 +1000,13 @@
         <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.145</v>
+        <v>0.4882</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5505</v>
+        <v>-0.0577</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4056</v>
+        <v>0.546</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7501</v>
+        <v>0.1593</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4801</v>
+        <v>-0.2932</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.27</v>
+        <v>0.4526</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2208</v>
+        <v>1.5123</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8643</v>
+        <v>-1.9927</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0851</v>
+        <v>3.505</v>
       </c>
       <c r="J8" t="n">
-        <v>1.189</v>
+        <v>3.2103</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1211</v>
+        <v>-0.5379</v>
       </c>
       <c r="L8" t="n">
-        <v>1.068</v>
+        <v>3.7482</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.698</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9853</v>
+        <v>-1.4548</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0171</v>
+        <v>-0.2431</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5853</v>
+        <v>0.647</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4975</v>
+        <v>-0.5302</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0878</v>
+        <v>1.1772</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0109</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7997</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3625</v>
+        <v>-3.7965</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3802</v>
+        <v>-5.6629</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0176</v>
+        <v>1.8664</v>
       </c>
       <c r="G9" t="n">
         <v>-6.2488</v>
@@ -1156,13 +1156,13 @@
         <v>2.3787</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2827</v>
+        <v>0.8488</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3889</v>
+        <v>-0.6715</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6716</v>
+        <v>1.5204</v>
       </c>
       <c r="V9" t="n">
         <v>1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.2477</v>
+        <v>-5.7279</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.8643</v>
+        <v>-6.4568</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6166</v>
+        <v>0.7289</v>
       </c>
       <c r="G10" t="n">
         <v>-6.0862</v>
@@ -1234,13 +1234,13 @@
         <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3509</v>
+        <v>0.1689</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5688</v>
+        <v>-0.1613</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2179</v>
+        <v>0.3303</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6036</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8916999999999984</v>
+        <v>0.04429999999999978</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.5273</v>
+        <v>-10.5912</v>
       </c>
       <c r="F11" t="n">
-        <v>10.6355</v>
+        <v>10.6356</v>
       </c>
       <c r="G11" t="n">
         <v>-10.8713</v>
@@ -1312,13 +1312,13 @@
         <v>16.8491</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5059</v>
+        <v>4.4419</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.0818</v>
+        <v>-2.146</v>
       </c>
       <c r="U11" t="n">
-        <v>6.587899999999999</v>
+        <v>6.5882</v>
       </c>
       <c r="V11" t="n">
         <v>4.491400000000001</v>
@@ -1327,7 +1327,7 @@
         <v>8.8421</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.350700000000001</v>
+        <v>-4.3507</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.263</v>
+        <v>6.7606</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2357</v>
+        <v>4.5413</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0274</v>
+        <v>2.2193</v>
       </c>
       <c r="G12" t="n">
         <v>7.7951</v>
@@ -1390,13 +1390,13 @@
         <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3319</v>
+        <v>-0.8343</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3103</v>
+        <v>-1.0047</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0215</v>
+        <v>0.1705</v>
       </c>
       <c r="V12" t="n">
         <v>0.1962</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.044</v>
+        <v>4.3849</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5725</v>
+        <v>2.5237</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4715</v>
+        <v>1.8612</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0125</v>
+        <v>5.0127</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6758</v>
+        <v>4.4981</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3367</v>
+        <v>0.5145</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9661</v>
+        <v>5.0968</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1867</v>
+        <v>4.4864</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7795</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9536</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4891</v>
+        <v>0.0118</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4428</v>
+        <v>-0.0959</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.2313</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4975</v>
+        <v>-0.5909</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5797</v>
+        <v>0.3596</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9774</v>
+        <v>4.0022</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1162</v>
+        <v>1.98</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8612</v>
+        <v>2.0223</v>
       </c>
       <c r="G14" t="n">
-        <v>5.0127</v>
+        <v>3.0125</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4981</v>
+        <v>2.6758</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5145</v>
+        <v>0.3367</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0968</v>
+        <v>3.9661</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4864</v>
+        <v>2.1867</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6104000000000001</v>
+        <v>1.7795</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.9536</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0118</v>
+        <v>0.4891</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0959</v>
+        <v>-1.4428</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5858</v>
+        <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6388</v>
+        <v>0.0403</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9984</v>
+        <v>-1.0901</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3596</v>
+        <v>1.1304</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5441</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>A. VAZQUEZ ASTILLEROS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3872</v>
+        <v>0.4103</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-1.0428</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2798</v>
+        <v>1.4531</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1329</v>
+        <v>1.6423</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0699</v>
+        <v>0.5596</v>
       </c>
       <c r="I16" t="n">
-        <v>0.063</v>
+        <v>1.0827</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1682</v>
+        <v>0.4705</v>
       </c>
       <c r="K16" t="n">
-        <v>0.128</v>
+        <v>0.3499</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0402</v>
+        <v>0.1205</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0353</v>
+        <v>1.1718</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0581</v>
+        <v>0.2096</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0228</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0562</v>
+        <v>-0.4213</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0696</v>
+        <v>-0.5221</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1258</v>
+        <v>0.1008</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ASTILLEROS</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0042</v>
+        <v>0.4036</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1446</v>
+        <v>-1.0963</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1488</v>
+        <v>1.4999</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6423</v>
+        <v>0.1329</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5596</v>
+        <v>0.0699</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0827</v>
+        <v>0.063</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4705</v>
+        <v>0.1682</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3499</v>
+        <v>0.128</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1205</v>
+        <v>0.0402</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1718</v>
+        <v>-0.0353</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2096</v>
+        <v>-0.0581</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8274</v>
+        <v>0.0725</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.624</v>
+        <v>-0.2734</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2035</v>
+        <v>0.3459</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0621</v>
+        <v>-0.2939</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2131</v>
+        <v>-0.4169</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1511</v>
+        <v>0.123</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7628</v>
@@ -1858,13 +1858,13 @@
         <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.2707</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3047</v>
+        <v>0.101</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1978</v>
+        <v>0.1697</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.414</v>
+        <v>-0.3579</v>
       </c>
       <c r="E19" t="n">
         <v>-0.5124</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0984</v>
+        <v>0.1546</v>
       </c>
       <c r="G19" t="n">
         <v>0.268</v>
@@ -1936,13 +1936,13 @@
         <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2856</v>
+        <v>-0.2294</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7362</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2799</v>
+        <v>-2.6873</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5437</v>
+        <v>1.8199</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1065</v>
@@ -2014,13 +2014,13 @@
         <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.156</v>
+        <v>-0.2873</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0072</v>
+        <v>-0.4147</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1488</v>
+        <v>0.1275</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2666</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5032</v>
+        <v>-1.9668</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0094</v>
+        <v>-1.4169</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4938</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.0058</v>
@@ -2092,13 +2092,13 @@
         <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.37</v>
+        <v>-0.0936</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0696</v>
+        <v>-0.4771</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4397</v>
+        <v>0.3835</v>
       </c>
       <c r="V21" t="n">
         <v>-2.0772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3689</v>
+        <v>-5.2318</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.6043</v>
+        <v>-6.2987</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2354</v>
+        <v>1.0669</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4672</v>
@@ -2170,13 +2170,13 @@
         <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6263</v>
+        <v>-0.4892</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4351</v>
+        <v>-1.1295</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8088</v>
+        <v>0.6403</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4737</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3052</v>
+        <v>-6.2785</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.5089</v>
+        <v>-6.8145</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2036</v>
+        <v>0.536</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2669</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6508</v>
+        <v>-0.6241</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6936</v>
+        <v>-0.9992</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0428</v>
+        <v>0.3752</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2071</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.891499999999998</v>
+        <v>1.5706</v>
       </c>
       <c r="E24" t="n">
         <v>-10.6355</v>
       </c>
       <c r="F24" t="n">
-        <v>11.5271</v>
+        <v>12.2063</v>
       </c>
       <c r="G24" t="n">
         <v>10.8712</v>
@@ -2299,7 +2299,7 @@
         <v>-1.2157</v>
       </c>
       <c r="J24" t="n">
-        <v>8.450800000000003</v>
+        <v>8.450799999999999</v>
       </c>
       <c r="K24" t="n">
         <v>10.6308</v>
@@ -2308,13 +2308,13 @@
         <v>-2.1799</v>
       </c>
       <c r="M24" t="n">
-        <v>2.4206</v>
+        <v>2.420599999999999</v>
       </c>
       <c r="N24" t="n">
         <v>1.4563</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9642000000000002</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="P24" t="n">
         <v>-1.9823</v>
@@ -2326,13 +2326,13 @@
         <v>14.8668</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.506</v>
+        <v>-2.827</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.587800000000001</v>
+        <v>-6.587899999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>3.082</v>
+        <v>3.7612</v>
       </c>
       <c r="V24" t="n">
         <v>-4.491400000000001</v>
